--- a/26년도_2주간_식단.xlsx
+++ b/26년도_2주간_식단.xlsx
@@ -10158,7 +10158,7 @@
    / 전분물(감자전분 2T + 물 3T) 따로
 [맑은 감자국]
 5. 감자 1개 나박 / 양파 1/4 / 대파 → 냉장
-6. 물 1L + 멸치·다시마육수(또는 코인육수)
+6. 물 1L + 멸치·다시마육수(멸치 10~12마리 + 다시마 1장)
 [브로콜리]
 7. 브로콜리 1개 한입크기 → 냉장</t>
         </is>
@@ -15057,7 +15057,7 @@
 5. 유부 5장 채썰기 / 팽이 1봉 밑동제거
    / 대파 1대 어슷 → 냉장
 6. 냄비에 물 1L + 멸치·다시마육수
-   (또는 코인육수) 세팅
+   (멸치 10~12마리 + 다시마 1장)
 [매쉬포테이토]
 7. 감자 3개 껍질 벗겨 큼직하게
    → 물에 담가 냉장</t>
@@ -15085,7 +15085,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="261" customHeight="1" s="90">
+    <row r="3" ht="321" customHeight="1" s="90">
       <c r="A3" s="119" t="inlineStr">
         <is>
           <t>수 (7/22)</t>
@@ -15093,42 +15093,47 @@
       </c>
       <c r="B3" s="120" t="inlineStr">
         <is>
-          <t>새우볶음밥
-+ 청경채 두부 맑은국
+          <t>새우 청경채 볶음밥
++ 맑은 무국
 + 김구이
 + 포도 (간식)</t>
         </is>
       </c>
       <c r="C3" s="120" t="inlineStr">
         <is>
-          <t>[새우볶음밥]
+          <t>[새우 청경채 볶음밥]
 1. 새우살 480g → 한입 크기
 2. 밑간: 청주 1T + 소금 + 후추 → 냉장
 3. 양파 1개 다지기 / 당근 1/3개 다지기
    / 대파 1대 송송 → 냉장
-4. 달걀 3개 풀어 냉장
-[청경채 두부 맑은국]
-5. 청경채 4~5포기 밑동 잘라 손질
-   / 두부 1/2모 깍둑 / 대파 조금 → 냉장
-6. 냄비에 물 1L + 멸치·다시마육수
-   (또는 코인육수) 세팅
+4. 청경채 4~5포기 → 밑동 자르고
+   1cm 폭으로 썰기 → 냉장
+5. 달걀 3개 풀어 냉장
+[맑은 무국]
+6. 무 1/4개 나박썰기 / 대파 어슷 → 냉장
+7. 육수 재료: 물 1L + 멸치 10~12마리
+   (머리·내장 제거) + 다시마 1장
 [김구이] 김 준비</t>
         </is>
       </c>
       <c r="D3" s="120" t="inlineStr">
         <is>
           <t>★ 식사 20분 전 시작
-[청경채 두부 맑은국 — 먼저]
-1. 육수 끓여 국간장 1T + 소금 간
-2. 두부 넣고 3분
-3. 청경채+대파 넣고 1~2분
-   (청경채 아삭하게) → 마무리
-[새우볶음밥 — 마지막]
-4. 팬에 기름, 새우 센불 1분 볶아 꺼내기
-5. 달걀 넣어 스크램블 → 밥 넣고 2분
-6. 양파·당근 넣고 1분
-7. 새우 다시 넣고 간장 1T+소금+후추
-8. 대파 넣고 참기름 마무리
+[맑은 무국 — 먼저]
+1. 물에 멸치·다시마 넣고 끓이기
+   → 끓기 시작하면 중불 7~8분 우린 뒤
+   멸치·다시마 건지기 (오래 끓이면 쓴맛)
+2. 무 넣고 중불 8분 (무가 투명해질 때까지)
+3. 국간장 1T + 다진마늘 + 소금 간
+4. 대파 넣어 마무리
+[새우 청경채 볶음밥 — 마지막]
+5. 팬에 기름, 새우 센불 1분 볶아 꺼내기
+6. 달걀 넣어 스크램블 → 밥 넣고 2분
+7. 양파·당근 넣고 1분
+8. 청경채 넣고 센불 1분 (숨만 죽이기)
+   ※ 청경채는 볶음으로! 국에는 넣지 않음
+9. 새우 다시 넣고 간장 1T + 소금 + 후추
+10. 대파 넣고 참기름 마무리
 [김구이] 김 살짝 구워 잘라 접시에
 [포도] 씻어서 접시에</t>
         </is>
